--- a/doc/help_dialogs/Input_files/autosave.xlsx
+++ b/doc/help_dialogs/Input_files/autosave.xlsx
@@ -259,7 +259,7 @@
     <t xml:space="preserve">~currtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Current date and time with seconds in format yy-MM-dd_hhmmss.  Not the same as roast time. </t>
+    <t xml:space="preserve">Current date and time with seconds in format yy-MM-dd_hhmmss. Not the same as roast time.</t>
   </si>
   <si>
     <t xml:space="preserve">21-01-18_093609</t>
@@ -520,7 +520,7 @@
     <t xml:space="preserve">~mode</t>
   </si>
   <si>
-    <t xml:space="preserve">From Config&gt;Temperature - the current temperature mode C or F.  </t>
+    <t xml:space="preserve">From Config&gt;Temperature - the current temperature mode C or F</t>
   </si>
   <si>
     <t xml:space="preserve">F</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">EXAMPLES</t>
   </si>
   <si>
-    <t xml:space="preserve">tn:Data used to replace the fields in the Autosave File Name Prefix are pulled from the current Roast Properties.  </t>
+    <t xml:space="preserve">tn:Data used to replace the fields in the Autosave File Name Prefix are pulled from the current Roast Properties.</t>
   </si>
   <si>
     <t xml:space="preserve">Autosave Field</t>
@@ -1199,7 +1199,7 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="76.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="104.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.11"/>
   </cols>
   <sheetData>
@@ -2022,7 +2022,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>194</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>200</v>
       </c>
